--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2394,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2407,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2373,7 +2417,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2510,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2523,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2533,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2571,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2626,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2639,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2605,7 +2649,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2643,12 +2687,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2706,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2742,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2803,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2858,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2919,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2938,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2974,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3035,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3054,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3090,2811 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1988,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2108,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2157,12 +2205,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,41 +2436,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2455,12 +2507,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2474,7 +2526,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2499,46 +2551,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2571,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2615,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2687,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2731,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2803,12 +2867,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2822,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2847,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2919,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2938,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2963,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3035,12 +3107,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3054,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3079,46 +3151,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3151,12 +3227,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3170,7 +3246,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3195,18 +3271,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3219,60 +3299,64 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3286,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3296,33 +3380,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3335,60 +3423,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3402,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3412,33 +3504,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3451,60 +3547,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3518,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3528,17 +3628,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3548,13 +3648,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3671,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3577,7 +3681,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3615,12 +3719,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3634,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3670,7 +3774,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3683,60 +3787,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3750,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3760,17 +3868,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3780,13 +3888,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3911,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3809,7 +3921,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3847,12 +3959,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3866,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3902,7 +4014,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3915,22 +4027,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3963,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3982,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4018,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4031,22 +4143,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4079,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4098,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4134,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4157,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4200,7 +4312,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4214,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4250,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4375,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4273,7 +4385,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4311,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4330,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4366,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4491,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4389,7 +4501,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4427,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4446,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4482,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4607,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4543,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4562,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4598,77 +4710,73 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4692,65 +4800,61 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4783,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4802,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4827,7 +4931,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4838,35 +4942,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4899,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4918,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4954,77 +5058,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5038,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5048,17 +5148,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5068,45 +5168,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5139,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5158,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5194,35 +5290,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5255,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5274,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5310,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5371,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5390,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5426,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5487,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5506,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5531,50 +5627,46 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5607,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5626,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5662,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5723,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5742,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5778,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5839,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5858,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5883,7 +5975,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5894,7 +5986,2391 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD66"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1645,24 +1645,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,32 +2068,32 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2123,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2180,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2243,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2276,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2359,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2392,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2416,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2479,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2512,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2536,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2599,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2632,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2656,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2719,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2752,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2776,17 +2812,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2796,7 +2832,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2839,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2872,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2896,37 +2936,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2992,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3031,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3046,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3151,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3161,12 +3201,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3179,22 +3219,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3232,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3246,7 +3286,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3276,87 +3316,83 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3370,7 +3406,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3380,17 +3416,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3405,82 +3441,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3526,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,107 +3536,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,7 +3646,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3628,65 +3656,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3719,12 +3747,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3766,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3763,88 +3791,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3886,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3868,65 +3896,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3959,12 +3987,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +4006,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4003,46 +4031,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4075,12 +4107,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4094,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,46 +4151,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4227,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,18 +4271,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4299,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4269,7 +4309,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4279,40 +4319,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4380,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4423,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4385,7 +4433,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4395,40 +4443,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4504,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4547,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4501,7 +4557,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4511,40 +4567,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4568,33 +4628,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4671,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4617,7 +4681,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4627,40 +4691,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4752,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4795,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4733,7 +4805,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4743,40 +4815,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4790,7 +4866,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4800,33 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4919,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4849,7 +4929,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4859,40 +4939,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +5000,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4955,7 +5043,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4965,7 +5053,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4975,40 +5063,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5032,33 +5124,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5071,52 +5167,56 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5124,7 +5224,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5148,33 +5248,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5187,60 +5291,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,33 +5372,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5303,60 +5415,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5486,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5380,33 +5496,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5419,60 +5539,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5610,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5496,17 +5620,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5516,13 +5640,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5535,60 +5663,64 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5602,7 +5734,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5612,17 +5744,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5632,13 +5764,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5651,60 +5787,64 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5858,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5728,33 +5868,37 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5911,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5777,7 +5921,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5815,12 +5959,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5834,7 +5978,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5870,7 +6014,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5883,7 +6027,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +6037,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5931,12 +6075,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5950,7 +6094,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5986,7 +6130,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5999,22 +6143,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6191,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6210,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6102,7 +6246,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6259,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6163,12 +6307,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6326,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6218,7 +6362,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6231,22 +6375,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6279,12 +6423,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6442,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6323,22 +6467,18 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6351,22 +6491,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6399,12 +6539,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6418,7 +6558,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6443,92 +6583,84 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6542,7 +6674,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6552,107 +6684,99 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6666,7 +6790,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6676,107 +6800,99 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6790,7 +6906,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6800,107 +6916,99 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6914,7 +7022,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6924,65 +7032,61 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7015,12 +7119,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7034,7 +7138,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7059,7 +7163,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7070,77 +7174,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7154,7 +7254,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7164,17 +7264,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7184,45 +7284,41 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7255,12 +7351,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7274,7 +7370,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7299,46 +7395,50 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7371,12 +7471,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7390,7 +7490,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7425,40 +7525,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7491,12 +7591,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7510,7 +7610,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7546,35 +7646,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7607,12 +7707,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7626,7 +7726,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7651,46 +7751,50 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7723,12 +7827,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7742,7 +7846,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7777,40 +7881,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7843,12 +7947,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7862,7 +7966,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7897,40 +8001,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7963,12 +8067,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7982,7 +8086,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8007,46 +8111,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8079,12 +8187,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8098,7 +8206,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8133,40 +8241,40 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8199,12 +8307,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8218,7 +8326,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8248,41 +8356,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8315,12 +8427,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8334,7 +8446,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8370,7 +8482,3495 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD95"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3119,32 +3119,36 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3176,17 +3180,17 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3196,17 +3200,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3276,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3392,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3512,7 +3516,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3566,7 +3570,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3756,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3806,7 +3810,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3876,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3921,12 +3925,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3996,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4156,17 +4160,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4236,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4480,7 +4484,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4728,7 +4732,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4852,7 +4856,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4976,7 +4980,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5100,7 +5104,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5224,7 +5228,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5472,7 +5476,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5596,7 +5600,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5844,7 +5848,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5931,32 +5935,36 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5964,7 +5972,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5988,33 +5996,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6092,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6196,7 +6208,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6312,7 +6324,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6428,7 +6440,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6544,7 +6556,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6660,7 +6672,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6776,7 +6788,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6892,7 +6904,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7008,7 +7020,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7124,7 +7136,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7240,7 +7252,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7356,7 +7368,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7476,7 +7488,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7596,7 +7608,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7712,7 +7724,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7832,7 +7844,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7952,7 +7964,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8072,7 +8084,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8192,7 +8204,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8312,7 +8324,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8432,7 +8444,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8548,7 +8560,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8668,7 +8680,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8735,22 +8747,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8783,12 +8795,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8837,82 +8849,78 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8926,7 +8934,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8936,107 +8944,103 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9050,7 +9054,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9060,22 +9064,22 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9085,12 +9089,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9107,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9113,7 +9117,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9133,24 +9137,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9160,7 +9164,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9174,7 +9178,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9209,12 +9213,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9231,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9237,7 +9241,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9257,24 +9261,24 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -9284,7 +9288,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9298,7 +9302,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9323,22 +9327,22 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9355,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9361,7 +9365,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9371,32 +9375,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9404,7 +9412,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9418,7 +9426,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9428,33 +9436,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9479,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9477,7 +9489,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9497,34 +9509,34 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9538,7 +9550,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9563,22 +9575,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9603,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9601,7 +9613,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9611,44 +9623,40 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9662,7 +9670,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9672,17 +9680,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9692,17 +9700,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9719,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9725,7 +9729,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9745,24 +9749,24 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9772,7 +9776,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9786,7 +9790,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9811,22 +9815,22 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9843,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9849,7 +9853,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9869,19 +9873,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9891,12 +9895,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9910,7 +9914,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9945,12 +9949,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9967,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9973,7 +9977,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9993,7 +9997,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -10015,12 +10019,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10034,7 +10038,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10059,22 +10063,22 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10091,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -10097,7 +10101,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -10107,40 +10111,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10154,7 +10162,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10164,22 +10172,22 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -10189,12 +10197,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10215,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10217,7 +10225,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10237,34 +10245,34 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10278,7 +10286,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10303,22 +10311,22 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10331,60 +10339,64 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10398,7 +10410,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10408,33 +10420,37 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10447,60 +10463,64 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10514,7 +10534,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10524,37 +10544,37 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10587,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10577,7 +10597,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10615,12 +10635,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10634,7 +10654,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10659,7 +10679,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10683,7 +10703,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10693,7 +10713,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10731,12 +10751,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10750,7 +10770,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10775,18 +10795,22 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10799,22 +10823,22 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10847,12 +10871,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10866,7 +10890,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10891,7 +10915,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10915,22 +10939,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10963,12 +10987,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10982,7 +11006,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -11031,22 +11055,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -11079,12 +11103,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11098,7 +11122,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11147,22 +11171,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -11200,7 +11224,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11214,7 +11238,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11263,7 +11287,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11273,7 +11297,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11311,12 +11335,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11330,7 +11354,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11355,22 +11379,18 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -11383,22 +11403,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -11431,12 +11451,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11450,7 +11470,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11475,22 +11495,18 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -11503,22 +11519,22 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11551,12 +11567,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11570,7 +11586,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11595,22 +11611,22 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11639,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11633,7 +11649,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11671,12 +11687,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11690,7 +11706,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11715,7 +11731,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11725,12 +11741,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11759,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11753,7 +11769,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11791,12 +11807,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11810,7 +11826,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11835,22 +11851,22 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11863,22 +11879,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11911,12 +11927,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11930,45 +11946,405 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC95" s="2" t="inlineStr">
+      <c r="AC98" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
         </is>
       </c>
-      <c r="AD95" s="2" t="inlineStr">
+      <c r="AD98" s="2" t="inlineStr">
         <is>
           <t>4/15</t>
         </is>

--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5808,17 +5808,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6676,17 +6676,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9811,32 +9811,36 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9844,7 +9848,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9868,17 +9872,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9888,7 +9892,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9931,32 +9935,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9964,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9988,17 +9996,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10008,17 +10016,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -10051,32 +10059,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10084,7 +10096,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10108,17 +10120,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10128,17 +10140,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -10171,32 +10183,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10204,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,17 +10244,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10248,12 +10264,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10324,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10444,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,17 +10504,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10832,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10860,12 +10876,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
@@ -10994,7 +11010,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11684,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11728,17 +11744,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -12056,7 +12072,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12100,12 +12116,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12180,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12224,12 +12240,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12300,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12544,7 +12560,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12588,12 +12604,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
@@ -12664,7 +12680,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12784,7 +12800,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12908,7 +12924,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12957,12 +12973,12 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13098,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13168,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13396,7 +13412,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13445,12 +13461,12 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13904,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -14012,7 +14028,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14056,12 +14072,12 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
@@ -14438,7 +14454,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14648,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -15008,7 +15024,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15052,17 +15068,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15148,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15256,7 +15272,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15300,12 +15316,12 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
@@ -15504,7 +15520,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15548,12 +15564,12 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
@@ -15628,7 +15644,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15752,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15796,12 +15812,12 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
@@ -16000,7 +16016,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16124,7 +16140,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16302,7 +16318,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16388,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16744,7 +16760,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -17046,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -17550,7 +17566,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17756,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17794,7 +17810,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -17988,7 +18004,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18032,12 +18048,12 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18166,7 +18182,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18252,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -19414,7 +19430,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19500,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19528,17 +19544,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19624,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19657,12 +19673,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19748,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19781,12 +19797,12 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19872,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19900,12 +19916,12 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -19980,7 +19996,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20034,7 +20050,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20116,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20144,12 +20160,12 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
@@ -20224,7 +20240,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20268,12 +20284,12 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
@@ -20348,7 +20364,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20472,7 +20488,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20596,7 +20612,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20774,7 +20790,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20860,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -21340,7 +21356,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21758,7 +21774,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21998,7 +22014,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -22200,7 +22216,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22297,24 +22313,24 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O177" s="2" t="inlineStr">
@@ -22324,7 +22340,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22373,12 +22389,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -22411,32 +22427,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22444,7 +22464,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22468,17 +22488,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22488,12 +22508,12 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
@@ -22541,24 +22561,24 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O179" s="2" t="inlineStr">
@@ -22568,7 +22588,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22617,12 +22637,12 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22655,32 +22675,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -22688,7 +22712,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22712,17 +22736,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22732,17 +22756,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22775,12 +22799,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22808,7 +22832,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22816,10 +22840,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="S181" s="2" t="inlineStr"/>
       <c r="T181" s="2" t="inlineStr"/>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22895,32 +22927,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22928,7 +22964,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22952,17 +22988,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -22972,12 +23008,12 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
@@ -23015,32 +23051,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -23048,7 +23088,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23072,17 +23112,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23092,12 +23132,12 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
@@ -23135,12 +23175,12 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -23168,7 +23208,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23176,10 +23216,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R184" s="2" t="inlineStr"/>
-      <c r="S184" s="2" t="inlineStr"/>
-      <c r="T184" s="2" t="inlineStr"/>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V184" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23288,7 +23344,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23342,7 +23398,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23408,7 +23464,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23495,32 +23551,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23528,7 +23588,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23552,17 +23612,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23572,12 +23632,12 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
@@ -23648,7 +23708,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23768,7 +23828,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23888,7 +23948,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24008,7 +24068,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24310,7 +24370,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -24678,7 +24738,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25180,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25169,12 +25229,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -25244,7 +25304,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25288,12 +25348,12 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25422,7 +25482,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -25616,7 +25676,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25660,17 +25720,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -25914,7 +25974,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -26224,7 +26284,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26268,17 +26328,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26408,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26392,12 +26452,12 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26472,7 +26532,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26521,7 +26581,7 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
@@ -26716,7 +26776,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26765,12 +26825,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -27010,7 +27070,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -27080,7 +27140,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27124,12 +27184,12 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27576,7 +27636,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27620,17 +27680,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -27700,7 +27760,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27749,7 +27809,7 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
@@ -27824,7 +27884,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27868,17 +27928,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -28072,7 +28132,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28116,12 +28176,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28196,7 +28256,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28240,12 +28300,12 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28564,7 +28624,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28608,17 +28668,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -28742,7 +28802,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28872,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28856,17 +28916,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -29060,7 +29120,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29104,12 +29164,12 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
@@ -29184,7 +29244,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29233,7 +29293,7 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
@@ -29432,7 +29492,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29476,7 +29536,7 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
@@ -29486,7 +29546,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -29610,7 +29670,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29794,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -30052,7 +30112,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30101,7 +30161,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30176,7 +30236,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30225,12 +30285,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30360,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30344,7 +30404,7 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
@@ -30354,7 +30414,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30484,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30468,12 +30528,12 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -30726,7 +30786,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -30850,7 +30910,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -30920,7 +30980,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -30964,17 +31024,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -31168,7 +31228,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31212,17 +31272,17 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -31292,7 +31352,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31341,12 +31401,12 @@
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -31536,7 +31596,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31580,12 +31640,12 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
@@ -31660,7 +31720,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31709,7 +31769,7 @@
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
@@ -31784,7 +31844,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31828,12 +31888,12 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
@@ -32032,7 +32092,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32076,7 +32136,7 @@
       </c>
       <c r="AB256" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC256" s="2" t="inlineStr">
@@ -32086,7 +32146,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32270,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -32528,7 +32588,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32572,17 +32632,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32766,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -32776,7 +32836,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32820,17 +32880,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -33148,7 +33208,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33197,12 +33257,12 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -33272,7 +33332,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33321,7 +33381,7 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33396,7 +33456,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33440,12 +33500,12 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33520,7 +33580,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33564,12 +33624,12 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33644,7 +33704,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33688,7 +33748,7 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
@@ -33698,7 +33758,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -34066,7 +34126,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -34260,7 +34320,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34304,17 +34364,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -34438,7 +34498,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -34508,7 +34568,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34552,17 +34612,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -34853,24 +34913,24 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O279" s="2" t="inlineStr">
@@ -34880,7 +34940,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34929,12 +34989,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -34977,12 +35037,12 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
@@ -35004,7 +35064,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35053,7 +35113,7 @@
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35211,32 +35271,36 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N282" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O282" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -35244,7 +35308,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35268,17 +35332,17 @@
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA282" s="2" t="inlineStr">
@@ -35288,12 +35352,12 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
@@ -35451,32 +35515,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35484,7 +35552,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35508,17 +35576,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35528,12 +35596,12 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35571,32 +35639,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -35604,7 +35676,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35628,17 +35700,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35648,7 +35720,7 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
@@ -35658,7 +35730,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -35691,32 +35763,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35724,7 +35800,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35748,17 +35824,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35768,17 +35844,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -35811,32 +35887,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35844,7 +35924,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35868,17 +35948,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35888,17 +35968,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -35964,7 +36044,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36008,12 +36088,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36084,7 +36164,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36128,7 +36208,7 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
@@ -36138,7 +36218,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-operations.xlsx
+++ b/data/export/2026-10-02-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5808,17 +5808,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6676,17 +6676,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10307,32 +10307,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10340,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10364,17 +10368,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10384,12 +10388,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10427,32 +10431,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10460,7 +10468,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10484,17 +10492,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10504,17 +10512,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11336,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11372,17 +11380,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11762,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11832,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11868,17 +11876,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12010,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12370,7 +12378,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12498,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12568,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12680,7 +12688,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12800,7 +12808,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12844,17 +12852,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13230,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13474,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13912,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13958,7 +13966,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14656,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14692,17 +14700,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15086,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15156,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15192,17 +15200,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15450,7 +15458,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15652,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15698,7 +15706,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15776,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15946,7 +15954,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16024,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16060,17 +16068,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -16140,7 +16148,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16442,7 +16450,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16768,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16814,7 +16822,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17694,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17942,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18260,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18296,17 +18304,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19562,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19810,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20116,7 +20124,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20418,7 +20426,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -20488,7 +20496,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20542,7 +20550,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20620,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20656,17 +20664,17 @@
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20868,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20904,17 +20912,17 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -21286,7 +21294,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -21356,7 +21364,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21410,7 +21418,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -21530,7 +21538,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22224,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22642,7 +22650,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22766,7 +22774,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22894,7 +22902,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23188,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -23208,7 +23216,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23278,7 +23286,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -23431,32 +23439,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -23464,7 +23476,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23488,17 +23500,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -23508,17 +23520,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23600,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23675,32 +23687,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23708,7 +23724,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23732,17 +23748,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23752,17 +23768,17 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -23795,32 +23811,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23828,7 +23848,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23852,17 +23872,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23872,17 +23892,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -23948,7 +23968,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24002,7 +24022,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24088,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24370,7 +24390,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -24738,7 +24758,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -25482,7 +25502,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -25974,7 +25994,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -26284,7 +26304,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26333,12 +26353,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26428,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26452,17 +26472,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -27070,7 +27090,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -27884,7 +27904,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27933,12 +27953,12 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -28132,7 +28152,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28176,17 +28196,17 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -28802,7 +28822,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -28872,7 +28892,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28921,12 +28941,12 @@
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29140,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29164,17 +29184,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -29492,7 +29512,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29670,7 +29690,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29814,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30380,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30786,7 +30806,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -30910,7 +30930,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31248,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31277,12 +31297,12 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -31844,7 +31864,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31888,17 +31908,17 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -32092,7 +32112,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32270,7 +32290,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -32766,7 +32786,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -32836,7 +32856,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32885,12 +32905,12 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33476,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33500,17 +33520,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -33704,7 +33724,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -34126,7 +34146,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -34498,7 +34518,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -34568,7 +34588,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34617,12 +34637,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -35552,7 +35572,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35596,17 +35616,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -35676,7 +35696,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35897,12 +35917,12 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
@@ -35924,7 +35944,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35973,12 +35993,12 @@
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -36011,32 +36031,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -36044,7 +36068,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36068,17 +36092,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36088,17 +36112,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -36164,7 +36188,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
